--- a/Control_Gastos_2026.xlsx
+++ b/Control_Gastos_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880A3AC6-27F3-4D7A-A117-F14C6E3C638B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D8260C-D66E-4964-88B7-A2336BD49162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Visión General" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="89">
   <si>
     <t>Visión General 2026</t>
   </si>
@@ -1461,7 +1461,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.96</c:v>
+                  <c:v>28.26</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>32.799999999999997</c:v>
@@ -1738,7 +1738,7 @@
                   <c:v>241.66000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>61.25</c:v>
+                  <c:v>66.55</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="P3" s="6">
         <f t="shared" ref="P3:P17" si="1">IFERROR(O3/$O$19,0)</f>
-        <v>6.3335233390335033E-2</v>
+        <v>6.280815249819427E-2</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P4" s="6">
         <f t="shared" si="1"/>
-        <v>6.3335233390335033E-2</v>
+        <v>6.280815249819427E-2</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="P5" s="6">
         <f t="shared" si="1"/>
-        <v>0.2337861802520742</v>
+        <v>0.23184059290895959</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="P6" s="6">
         <f t="shared" si="1"/>
-        <v>3.0875926277788332E-2</v>
+        <v>3.0618974342869705E-2</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J8" s="4">
         <f>SUMIF(Agosto!$C$3:$C$32,$A8,Agosto!$E$3:$E$32)</f>
-        <v>7</v>
+        <v>12.3</v>
       </c>
       <c r="K8" s="4">
         <f>SUMIF(Septiembre!$C$3:$C$32,$A8,Septiembre!$E$3:$E$32)</f>
@@ -2970,11 +2970,11 @@
       </c>
       <c r="O8" s="5">
         <f t="shared" si="0"/>
-        <v>22.96</v>
+        <v>28.26</v>
       </c>
       <c r="P8" s="6">
         <f t="shared" si="1"/>
-        <v>3.6354423966052311E-2</v>
+        <v>4.4373959739974253E-2</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="P9" s="6">
         <f t="shared" si="1"/>
-        <v>5.1934891380074726E-2</v>
+        <v>5.1502685048519292E-2</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P13" s="6">
         <f t="shared" si="1"/>
-        <v>2.3750712521375637E-2</v>
+        <v>2.3553057186822848E-2</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="P15" s="6">
         <f t="shared" si="1"/>
-        <v>0.37573627208816263</v>
+        <v>0.37260936469553751</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="P16" s="6">
         <f t="shared" si="1"/>
-        <v>4.1722084995883209E-2</v>
+        <v>4.1374870458185477E-2</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P17" s="6">
         <f t="shared" si="1"/>
-        <v>7.9169041737918791E-2</v>
+        <v>7.8510190622742837E-2</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="J19" s="8">
         <f t="shared" si="2"/>
-        <v>67.599999999999994</v>
+        <v>72.899999999999991</v>
       </c>
       <c r="K19" s="8">
         <f t="shared" si="2"/>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="O19" s="8">
         <f t="shared" si="2"/>
-        <v>631.56000000000006</v>
+        <v>636.86</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="J21" s="10">
         <f t="shared" si="3"/>
-        <v>61.25</v>
+        <v>66.55</v>
       </c>
       <c r="K21" s="10">
         <f t="shared" si="3"/>
@@ -3864,7 +3864,7 @@
         <v>Videojuegos</v>
       </c>
       <c r="H3" s="18">
-        <f t="shared" ref="H3:H17" si="0">SUMIF($C$3:$C$32,G3,$E$3:$E$32)</f>
+        <f>SUMIF($C$3:$C$32,G3,$E$3:$E$32)</f>
         <v>40</v>
       </c>
       <c r="I3" s="19" t="str">
@@ -3894,7 +3894,7 @@
         <v>Apuestas</v>
       </c>
       <c r="H4" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G4,$E$3:$E$32)</f>
         <v>40</v>
       </c>
       <c r="I4" s="19" t="str">
@@ -3924,7 +3924,7 @@
         <v>Salidas/Ocio</v>
       </c>
       <c r="H5" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G5,$E$3:$E$32)</f>
         <v>122.4</v>
       </c>
       <c r="I5" s="19" t="str">
@@ -3955,7 +3955,7 @@
         <v>Suscripciones ocio</v>
       </c>
       <c r="H6" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G6,$E$3:$E$32)</f>
         <v>8.5</v>
       </c>
       <c r="I6" s="19" t="str">
@@ -3985,7 +3985,7 @@
         <v>Viajes</v>
       </c>
       <c r="H7" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G7,$E$3:$E$32)</f>
         <v>0</v>
       </c>
       <c r="I7" s="19" t="str">
@@ -4015,7 +4015,7 @@
         <v>Padel</v>
       </c>
       <c r="H8" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G8,$E$3:$E$32)</f>
         <v>15.96</v>
       </c>
       <c r="I8" s="19" t="str">
@@ -4045,7 +4045,7 @@
         <v>Alimentación</v>
       </c>
       <c r="H9" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G9,$E$3:$E$32)</f>
         <v>14.8</v>
       </c>
       <c r="I9" s="19" t="str">
@@ -4075,7 +4075,7 @@
         <v>Vivienda/Alquiler</v>
       </c>
       <c r="H10" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G10,$E$3:$E$32)</f>
         <v>0</v>
       </c>
       <c r="I10" s="19" t="str">
@@ -4105,7 +4105,7 @@
         <v>Transporte</v>
       </c>
       <c r="H11" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G11,$E$3:$E$32)</f>
         <v>0</v>
       </c>
       <c r="I11" s="19" t="str">
@@ -4135,7 +4135,7 @@
         <v>Salud</v>
       </c>
       <c r="H12" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G12,$E$3:$E$32)</f>
         <v>0</v>
       </c>
       <c r="I12" s="19" t="str">
@@ -4165,7 +4165,7 @@
         <v>Barbero</v>
       </c>
       <c r="H13" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G13,$E$3:$E$32)</f>
         <v>15</v>
       </c>
       <c r="I13" s="19" t="str">
@@ -4195,7 +4195,7 @@
         <v>Otros</v>
       </c>
       <c r="H14" s="21">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G14,$E$3:$E$32)</f>
         <v>0</v>
       </c>
       <c r="I14" s="22" t="str">
@@ -4226,7 +4226,7 @@
         <v>Burocracia</v>
       </c>
       <c r="H15" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G15,$E$3:$E$32)</f>
         <v>237.3</v>
       </c>
       <c r="I15" s="22" t="str">
@@ -4256,7 +4256,7 @@
         <v>Regalos</v>
       </c>
       <c r="H16" s="18">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G16,$E$3:$E$32)</f>
         <v>20</v>
       </c>
       <c r="I16" s="22" t="str">
@@ -4286,7 +4286,7 @@
         <v>Multas</v>
       </c>
       <c r="H17" s="24">
-        <f t="shared" si="0"/>
+        <f>SUMIF($C$3:$C$32,G17,$E$3:$E$32)</f>
         <v>50</v>
       </c>
       <c r="I17" s="22" t="str">
@@ -4363,14 +4363,6 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16" t="str">
-        <f>IFERROR(INDEX(Categorías!$B$2:$B$16,MATCH(C21,Categorías!$A$2:$A$16,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="17"/>
       <c r="G21" s="25" t="s">
         <v>20</v>
       </c>
@@ -4501,7 +4493,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3:E32">
+  <conditionalFormatting sqref="E3:E20 E22:E32">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -4528,7 +4520,7 @@
               <x14:negativeFillColor rgb="FFFC605C"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E3:E32</xm:sqref>
+          <xm:sqref>E3:E20 E22:E32</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4755,7 +4747,7 @@
       </c>
       <c r="H8" s="18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>12.3</v>
       </c>
       <c r="I8" s="19" t="str">
         <f>Categorías!B7</f>
@@ -4822,14 +4814,22 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="A11" s="14">
+        <v>46260</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>48</v>
+      </c>
       <c r="D11" s="16" t="str">
         <f>IFERROR(INDEX(Categorías!$B$2:$B$16,MATCH(C11,Categorías!$A$2:$A$16,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="17"/>
+        <v>Ocio</v>
+      </c>
+      <c r="E11" s="17">
+        <v>5.3</v>
+      </c>
       <c r="G11" s="3" t="str">
         <f>Categorías!A10</f>
         <v>Transporte</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="H19" s="26">
         <f>SUMIF($I$3:$I$17,"Ocio",$H$3:$H$17)</f>
-        <v>61.25</v>
+        <v>66.55</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="H22" s="28">
         <f>SUM($E$3:$E$32)</f>
-        <v>67.599999999999994</v>
+        <v>72.899999999999991</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5158,8 +5158,8 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E8 E3 E10:E32">
-    <cfRule type="dataBar" priority="8">
+  <conditionalFormatting sqref="E5:E8 E3 E10 E12:E32">
+    <cfRule type="dataBar" priority="9">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5173,7 +5173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5186,8 +5186,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E8 E10:E1048576">
-    <cfRule type="dataBar" priority="3">
+  <conditionalFormatting sqref="E1:E8 E10 E12:E1048576">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5201,7 +5201,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5215,7 +5215,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5224,6 +5224,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{22AA725C-0A93-4302-B8D5-27ADF8BDC9B9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFC605C"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6353658C-50C0-43A0-AA63-D1E378187AED}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5241,7 +5255,7 @@
               <x14:negativeFillColor rgb="FFFC605C"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E5:E8 E3 E10:E32</xm:sqref>
+          <xm:sqref>E5:E8 E3 E10 E12:E32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{F4EF5B99-CA4B-44F6-A964-BD7FF0AF5FFE}">
@@ -5264,7 +5278,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E1:E8 E10:E1048576</xm:sqref>
+          <xm:sqref>E1:E8 E10 E12:E1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DE786F3A-6159-4CD3-918F-AB2546A03817}">
@@ -5288,6 +5302,16 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>E9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6353658C-50C0-43A0-AA63-D1E378187AED}">
+            <x14:dataBar axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:negativeFillColor rgb="FFFC605C"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E11</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
